--- a/src/test/resources/users.xlsx
+++ b/src/test/resources/users.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="7">
   <si>
     <t>Password</t>
   </si>
@@ -24,19 +24,13 @@
     <t>Email</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Mi@12345678</t>
+  </si>
+  <si>
     <t>m.hneef@student.aaup.edu</t>
-  </si>
-  <si>
-    <t>Mi12345678</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Mi@12345678</t>
-  </si>
-  <si>
-    <t>misk haneef</t>
   </si>
   <si>
     <t>Pass</t>
@@ -409,46 +403,32 @@
         <v>0</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C2" t="s" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>7</v>
-      </c>
+      <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1"/>
-    <hyperlink ref="A4" r:id="rId2"/>
-    <hyperlink ref="B4" r:id="rId3"/>
-    <hyperlink ref="A2" r:id="rId4" display="m.hneef@student.aaup.edu"/>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="B2" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/users.xlsx
+++ b/src/test/resources/users.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="7">
   <si>
     <t>Password</t>
   </si>

--- a/src/test/resources/users.xlsx
+++ b/src/test/resources/users.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="7">
   <si>
     <t>Password</t>
   </si>
